--- a/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
+++ b/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
+++ b/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
+++ b/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
+++ b/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
+++ b/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
+++ b/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
+++ b/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -624,7 +624,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/CodeSystem/not-medication-reason-cs</t>
+    <t>http://tecnomod-um.org/ValueSet/not-medication-reason-vs</t>
   </si>
   <si>
     <t>Event.statusReason</t>

--- a/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
+++ b/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/anticoagulant-reversal-medication-administration-profile</t>
+    <t>http://qualityregistry.org/StructureDefinition/anticoagulant-reversal-medication-administration-profile</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/stroke-medication-administration-profile</t>
+    <t>http://qualityregistry.org/StructureDefinition/stroke-medication-administration-profile</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -466,7 +466,7 @@
     <t>requiredPostAcuteCare</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://tecnomod-um.org/StructureDefinition/required-post-acute-care-ext}
+    <t xml:space="preserve">Extension {http://qualityregistry.org/StructureDefinition/required-post-acute-care-ext}
 </t>
   </si>
   <si>
@@ -482,7 +482,7 @@
     <t>assessmentTiming</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://tecnomod-um.org/StructureDefinition/assessment-timing-ext}
+    <t xml:space="preserve">Extension {http://qualityregistry.org/StructureDefinition/assessment-timing-ext}
 </t>
   </si>
   <si>
@@ -624,7 +624,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/not-medication-reason-vs</t>
+    <t>http://qualityregistry.org/ValueSet/not-medication-reason-vs</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -673,7 +673,7 @@
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the medication resource is recommended.  For example, if you require form or lot number, then you must reference the Medication resource.</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/anticoagulant-reversal-vs</t>
+    <t>http://qualityregistry.org/ValueSet/anticoagulant-reversal-vs</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -691,7 +691,7 @@
     <t>MedicationAdministration.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/resq-patient-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/resq-patient-profile)
 </t>
   </si>
   <si>
@@ -716,7 +716,7 @@
     <t>MedicationAdministration.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/stroke-encounter-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/stroke-encounter-profile)
 </t>
   </si>
   <si>

--- a/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
+++ b/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
+++ b/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -489,7 +489,7 @@
     <t>Timing category for medication administration</t>
   </si>
   <si>
-    <t>Timing category used by medication-administration builders, e.g. insulin within one hour or paracetamol timing. The Python code contains a typo variant tecnomod-um-org; this IG normalizes to tecnomod-um.org.</t>
+    <t>Timing category used by medication-administration builders, e.g. insulin within one hour or paracetamol timing. The Python code contains a typo variant tecnomod-um-org; this IG normalizes it to the qualityregistry.org canonical.</t>
   </si>
   <si>
     <t>MedicationAdministration.modifierExtension</t>

--- a/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
+++ b/StructureDefinition-anticoagulant-reversal-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
